--- a/data/product-tracker.xlsx
+++ b/data/product-tracker.xlsx
@@ -506,7 +506,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPP-04</t>
+          <t>OPPORTUNITY-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEC-0028</t>
+          <t>DECISION-0028</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEC-0031</t>
+          <t>DECISION-0031</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-02</t>
+          <t>EXPERIMENT-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -670,12 +670,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLOCK-01</t>
+          <t>BLOCKER-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POL-03 sign-off for LATAM accounts</t>
+          <t>POLICY-03 sign-off for LATAM accounts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REQ-G01</t>
+          <t>REQUEST-G01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P-GAB</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REQ-R01</t>
+          <t>REQUEST-R01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P-RUI</t>
+          <t>Rui Bastos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REQ-T01</t>
+          <t>REQUEST-T01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P-TOM</t>
+          <t>Tomas Silva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -811,14 +811,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Same as BLOCK-01</t>
+          <t>Same as BLOCKER-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REQ-A01</t>
+          <t>REQUEST-A01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Review DEC-0031 migration progress</t>
+          <t>Review DECISION-0031 migration progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/product-tracker.xlsx
+++ b/data/product-tracker.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Expand the Assist pilot</t>
+          <t>Expand the portal rollout</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
